--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-01).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-01).xlsx
@@ -912,45 +912,48 @@
   </si>
   <si>
     <t>214
-180</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>R$ 1.105.388,16</t>
-  </si>
-  <si>
-    <t>R$ 5.787,37
-R$ 5.927,65</t>
-  </si>
-  <si>
-    <t>3.3%
-5.6%</t>
-  </si>
-  <si>
-    <t>61.6</t>
+181</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>R$ 1.114.227,94</t>
+  </si>
+  <si>
+    <t>R$ 5.803,27
+R$ 5.943,73</t>
+  </si>
+  <si>
+    <t>3.4%
+5.7%</t>
+  </si>
+  <si>
+    <t>61.8</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>245.0%</t>
+  </si>
+  <si>
+    <t>202.2%</t>
+  </si>
+  <si>
+    <t>3.1%</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>246.1%</t>
-  </si>
-  <si>
-    <t>203.3%</t>
-  </si>
-  <si>
-    <t>3.1%</t>
-  </si>
-  <si>
     <t>29.8</t>
   </si>
   <si>
-    <t>62.7%</t>
-  </si>
-  <si>
-    <t>16.9%</t>
+    <t>62.4%</t>
+  </si>
+  <si>
+    <t>16.8%</t>
   </si>
   <si>
     <t>6.0</t>
@@ -959,19 +962,19 @@
     <t>8.5</t>
   </si>
   <si>
-    <t>14.7</t>
-  </si>
-  <si>
-    <t>21.3</t>
-  </si>
-  <si>
-    <t>63.4%</t>
+    <t>14.6</t>
+  </si>
+  <si>
+    <t>21.2</t>
+  </si>
+  <si>
+    <t>63.3%</t>
   </si>
   <si>
     <t>-R$ 34.019,48</t>
   </si>
   <si>
-    <t>2.97</t>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -8789,7 +8792,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8825,27 +8828,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
+      <c r="O58" s="5">
+        <v>8839.7800000000007</v>
+      </c>
+      <c r="P58" s="5">
+        <v>8839.7800000000007</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0.26651670582841436</v>
+      </c>
+      <c r="R58" s="7">
+        <v>94</v>
+      </c>
+      <c r="S58" s="6">
+        <v>0.22077922077922074</v>
+      </c>
+      <c r="T58" s="6">
+        <v>1.0355840643092928</v>
+      </c>
+      <c r="U58" s="6">
+        <v>0.61448082418340721</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.011809400233942472</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.0012011045523757377</v>
+      </c>
+      <c r="X58" s="8">
+        <v>27.992193670886074</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.31645569620253167</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.075949367088607597</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>3.8292118279569891</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>9.1102564102564099</v>
+      </c>
       <c r="AC58" s="8">
         <v>12.939579999999999</v>
       </c>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="AD58" s="8">
+        <v>19.676370886075947</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.59493670886075944</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>0</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -15488,7 +15525,7 @@
         <v>0</v>
       </c>
       <c r="AH111" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI111" s="11"/>
       <c r="AJ111" s="13">
@@ -15841,7 +15878,7 @@
         <v>-363.60000000000002</v>
       </c>
       <c r="AH114" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI114" s="11"/>
       <c r="AJ114" s="13">
@@ -16990,7 +17027,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17383,7 +17420,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18560,7 +18597,7 @@
         <v>-35</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -20878,7 +20915,7 @@
         <v>0</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -22172,7 +22209,7 @@
         <v>-143.30000000000001</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -24248,7 +24285,9 @@
       <c r="AB179" s="8">
         <v>1.2722208333333334</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>4.9222219999999997</v>
+      </c>
       <c r="AD179" s="8">
         <v>11.881945833333333</v>
       </c>
@@ -28333,7 +28372,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
@@ -28684,41 +28723,41 @@
         <v>309</v>
       </c>
       <c t="s" r="W216" s="14">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c t="s" r="X216" s="14">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="Y216" s="14">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="Z216" s="14">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="AA216" s="14">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="AB216" s="14">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="AC216" s="14">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="AD216" s="14">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="AE216" s="14">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AF216" s="14"/>
       <c t="s" r="AG216" s="14">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="AH216" s="14">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="AI216" s="14">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ216" s="15"/>
       <c t="s" r="AK216" s="15">
@@ -28728,10 +28767,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="AN216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO216" s="15"/>
       <c r="AP216" s="15"/>
